--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T08:08:15+00:00</t>
+    <t>2026-05-18T14:11:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:11:29+00:00</t>
+    <t>2026-05-21T09:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T09:18:21+00:00</t>
+    <t>2026-06-01T14:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:41:15+00:00</t>
+    <t>2026-06-01T15:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T15:18:33+00:00</t>
+    <t>2026-06-02T07:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$71</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2984" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2586" uniqueCount="449">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T07:35:19+00:00</t>
+    <t>2026-06-04T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -572,6 +572,15 @@
     <t>A selector of the type of consent being presented: ADR, Privacy, Treatment, Research.  This list is now extensible.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/consentscope"/&gt;
+    &lt;code value="adr"/&gt;
+    &lt;display value="Advance Directive"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>extensible</t>
   </si>
   <si>
@@ -581,7 +590,191 @@
     <t>http://hl7.org/fhir/ValueSet/consent-scope|4.0.1</t>
   </si>
   <si>
-    <t>Consent.scope.id</t>
+    <t>Consent.category</t>
+  </si>
+  <si>
+    <t>Classification of the consent statement - for indexing/retrieval</t>
+  </si>
+  <si>
+    <t>A classification of the type of consents found in the statement. This element supports indexing and retrieval of consent statements.</t>
+  </si>
+  <si>
+    <t>A classification of the type of consents found in a consent statement.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/consent-category|4.0.1</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>HL7 Table 0497 - Consent Type</t>
+  </si>
+  <si>
+    <t>CNTRCT</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Consent.patient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Patient|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Who the consent applies to</t>
+  </si>
+  <si>
+    <t>The patient/healthcare consumer to whom this consent applies.</t>
+  </si>
+  <si>
+    <t>Commonly, the patient the consent pertains to is the author, but for young and old people, it may be some other person.</t>
+  </si>
+  <si>
+    <t>Event.subject</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>Consent.dateTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Date de la directive anticipée</t>
+  </si>
+  <si>
+    <t>When this  Consent was issued / created / indexed.</t>
+  </si>
+  <si>
+    <t>This is not the time of the original consent, but the time that this statement was made or derived.</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>Field 13/ Consent Decision Date</t>
+  </si>
+  <si>
+    <t>FinancialConsent effectiveTime</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>Consent.performer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">consentor
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|RelatedPerson|4.0.1|PractitionerRole|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Who is agreeing to the policy and rules</t>
+  </si>
+  <si>
+    <t>Either the Grantor, which is the entity responsible for granting the rights listed in a Consent Directive or the Grantee, which is the entity responsible for complying with the Consent Directive, including any obligations or limitations on authorizations and enforcement of prohibitions.</t>
+  </si>
+  <si>
+    <t>Commonly, the patient the consent pertains to is the consentor, but particularly for young and old people, it may be some other person - e.g. a legal guardian.</t>
+  </si>
+  <si>
+    <t>Event.performer</t>
+  </si>
+  <si>
+    <t>Field 24/ ConsenterID</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>Consent.organization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">custodian
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Custodian of the consent</t>
+  </si>
+  <si>
+    <t>The organization that manages the consent, and the framework within which it is executed.</t>
+  </si>
+  <si>
+    <t>FiveWs.witness</t>
+  </si>
+  <si>
+    <t>Consent.source[x]</t>
+  </si>
+  <si>
+    <t>Attachment
+Reference(Consent|4.0.1|DocumentReference|4.0.1|Contract|4.0.1|QuestionnaireResponse|4.0.1)</t>
+  </si>
+  <si>
+    <t>Documents</t>
+  </si>
+  <si>
+    <t>The source on which this consent statement is based. The source might be a scanned original paper form, or a reference to a consent that links back to such a source, a reference to a document repository (e.g. XDS) that stores the original consent document.</t>
+  </si>
+  <si>
+    <t>The source can be contained inline (Attachment), referenced directly (Consent), referenced in a consent repository (DocumentReference), or simply by an identifier (Identifier), e.g. a CDA document id.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>Field 19 Informational Material Supplied Indicator</t>
+  </si>
+  <si>
+    <t>Consent.source[x]:sourceReference</t>
+  </si>
+  <si>
+    <t>sourceReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-document-reference-document)
+</t>
+  </si>
+  <si>
+    <t>Référence à un document externe</t>
+  </si>
+  <si>
+    <t>Consent.source[x]:sourceAttachment</t>
+  </si>
+  <si>
+    <t>sourceAttachment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attachment
+</t>
+  </si>
+  <si>
+    <t>Document encapsulé en B64</t>
+  </si>
+  <si>
+    <t>Consent.source[x]:sourceAttachment.id</t>
+  </si>
+  <si>
+    <t>Consent.source[x].id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -600,7 +793,10 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>Consent.scope.extension</t>
+    <t>Consent.source[x]:sourceAttachment.extension</t>
+  </si>
+  <si>
+    <t>Consent.source[x].extension</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -616,695 +812,324 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>Consent.scope.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
+    <t>Consent.source[x]:sourceAttachment.contentType</t>
+  </si>
+  <si>
+    <t>Consent.source[x].contentType</t>
+  </si>
+  <si>
+    <t>Mime type of the content, with charset etc.</t>
+  </si>
+  <si>
+    <t>Identifies the type of the data in the attachment and allows a method to be chosen to interpret or render the data. Includes mime type parameters such as charset where appropriate.</t>
+  </si>
+  <si>
+    <t>Processors of the data need to be able to know how to interpret the data.</t>
+  </si>
+  <si>
+    <t>text/plain; charset=UTF-8, image/png</t>
+  </si>
+  <si>
+    <t>The mime type of an attachment. Any valid mime type is allowed.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/mimetypes|4.0.1</t>
+  </si>
+  <si>
+    <t>Attachment.contentType</t>
+  </si>
+  <si>
+    <t>ED.2+ED.3/RP.2+RP.3. Note conversion may be needed if old style values are being used</t>
+  </si>
+  <si>
+    <t>./mediaType, ./charset</t>
+  </si>
+  <si>
+    <t>Consent.source[x]:sourceAttachment.language</t>
+  </si>
+  <si>
+    <t>Consent.source[x].language</t>
+  </si>
+  <si>
+    <t>Human language of the content (BCP-47)</t>
+  </si>
+  <si>
+    <t>The human language of the content. The value can be any valid value according to BCP 47.</t>
+  </si>
+  <si>
+    <t>Users need to be able to choose between the languages in a set of attachments.</t>
+  </si>
+  <si>
+    <t>en-AU</t>
+  </si>
+  <si>
+    <t>Attachment.language</t>
+  </si>
+  <si>
+    <t>./language</t>
+  </si>
+  <si>
+    <t>Consent.source[x]:sourceAttachment.data</t>
+  </si>
+  <si>
+    <t>Consent.source[x].data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">base64Binary
 </t>
   </si>
   <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Consent.scope.coding.id</t>
-  </si>
-  <si>
-    <t>Consent.scope.coding.extension</t>
-  </si>
-  <si>
-    <t>Consent.scope.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/consentscope</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Consent.scope.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Consent.scope.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>adr</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>Consent.scope.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Advance Directive</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Consent.scope.coding.userSelected</t>
+    <t>Representation en B64</t>
+  </si>
+  <si>
+    <t>The actual data of the attachment - a sequence of bytes, base64 encoded.</t>
+  </si>
+  <si>
+    <t>The base64-encoded data SHALL be expressed in the same character set as the base resource XML or JSON.</t>
+  </si>
+  <si>
+    <t>The data needs to able to be transmitted inline.</t>
+  </si>
+  <si>
+    <t>Attachment.data</t>
+  </si>
+  <si>
+    <t>ED.5</t>
+  </si>
+  <si>
+    <t>./data</t>
+  </si>
+  <si>
+    <t>Consent.source[x]:sourceAttachment.url</t>
+  </si>
+  <si>
+    <t>Consent.source[x].url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">url
+</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>A location where the data can be accessed.</t>
+  </si>
+  <si>
+    <t>If both data and url are provided, the url SHALL point to the same content as the data contains. Urls may be relative references or may reference transient locations such as a wrapping envelope using cid: though this has ramifications for using signatures. Relative URLs are interpreted relative to the service url, like a resource reference, rather than relative to the resource itself. If a URL is provided, it SHALL resolve to actual data.</t>
+  </si>
+  <si>
+    <t>The data needs to be transmitted by reference.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/logo-small.png</t>
+  </si>
+  <si>
+    <t>Attachment.url</t>
+  </si>
+  <si>
+    <t>RP.1+RP.2 - if they refer to a URL (see v2.6)</t>
+  </si>
+  <si>
+    <t>./reference/literal</t>
+  </si>
+  <si>
+    <t>Consent.source[x]:sourceAttachment.size</t>
+  </si>
+  <si>
+    <t>Consent.source[x].size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unsignedInt
+</t>
+  </si>
+  <si>
+    <t>Number of bytes of content (if url provided)</t>
+  </si>
+  <si>
+    <t>The number of bytes of data that make up this attachment (before base64 encoding, if that is done).</t>
+  </si>
+  <si>
+    <t>The number of bytes is redundant if the data is provided as a base64binary, but is useful if the data is provided as a url reference.</t>
+  </si>
+  <si>
+    <t>Representing the size allows applications to determine whether they should fetch the content automatically in advance, or refuse to fetch it at all.</t>
+  </si>
+  <si>
+    <t>Attachment.size</t>
+  </si>
+  <si>
+    <t>N/A (needs data type R3 proposal)</t>
+  </si>
+  <si>
+    <t>Consent.source[x]:sourceAttachment.hash</t>
+  </si>
+  <si>
+    <t>Consent.source[x].hash</t>
+  </si>
+  <si>
+    <t>Hash of the data (sha-1, base64ed)</t>
+  </si>
+  <si>
+    <t>The calculated hash of the data using SHA-1. Represented using base64.</t>
+  </si>
+  <si>
+    <t>The hash is calculated on the data prior to base64 encoding, if the data is based64 encoded. The hash is not intended to support digital signatures. Where protection against malicious threats a digital signature should be considered, see [Provenance.signature](http://hl7.org/fhir/R4/provenance-definitions.html#Provenance.signature) for mechanism to protect a resource with a digital signature.</t>
+  </si>
+  <si>
+    <t>Included so that applications can verify that the contents of a location have not changed due to technical failures (e.g., storage rot, transport glitch, incorrect version).</t>
+  </si>
+  <si>
+    <t>Attachment.hash</t>
+  </si>
+  <si>
+    <t>.integrityCheck[parent::ED/integrityCheckAlgorithm="SHA-1"]</t>
+  </si>
+  <si>
+    <t>Consent.source[x]:sourceAttachment.title</t>
+  </si>
+  <si>
+    <t>Consent.source[x].title</t>
+  </si>
+  <si>
+    <t>Label to display in place of the data</t>
+  </si>
+  <si>
+    <t>A label or set of text to display in place of the data.</t>
+  </si>
+  <si>
+    <t>Applications need a label to display to a human user in place of the actual data if the data cannot be rendered or perceived by the viewer.</t>
+  </si>
+  <si>
+    <t>Official Corporate Logo</t>
+  </si>
+  <si>
+    <t>Attachment.title</t>
+  </si>
+  <si>
+    <t>./title/data</t>
+  </si>
+  <si>
+    <t>Consent.source[x]:sourceAttachment.creation</t>
+  </si>
+  <si>
+    <t>Consent.source[x].creation</t>
+  </si>
+  <si>
+    <t>Date attachment was first created</t>
+  </si>
+  <si>
+    <t>The date that the attachment was first created.</t>
+  </si>
+  <si>
+    <t>This is often tracked as an integrity issue for use of the attachment.</t>
+  </si>
+  <si>
+    <t>Attachment.creation</t>
+  </si>
+  <si>
+    <t>Consent.policy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Policies covered by this consent</t>
+  </si>
+  <si>
+    <t>The references to the policies that are included in this consent scope. Policies may be organizational, but are often defined jurisdictionally, or in law.</t>
+  </si>
+  <si>
+    <t>Consent.policy.id</t>
+  </si>
+  <si>
+    <t>Consent.policy.extension</t>
+  </si>
+  <si>
+    <t>Consent.policy.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>Consent.policy.authority</t>
+  </si>
+  <si>
+    <t>Enforcement source for policy</t>
+  </si>
+  <si>
+    <t>Entity or Organization having regulatory jurisdiction or accountability for  enforcing policies pertaining to Consent Directives.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ppc-1
+</t>
+  </si>
+  <si>
+    <t>Consent.policy.uri</t>
+  </si>
+  <si>
+    <t>Specific policy covered by this consent</t>
+  </si>
+  <si>
+    <t>This element is for discoverability / documentation and does not modify or qualify the policy rules.</t>
+  </si>
+  <si>
+    <t>Consent.policyRule</t>
+  </si>
+  <si>
+    <t>Regulation that this consents to</t>
+  </si>
+  <si>
+    <t>A reference to the specific base computable regulation or policy.</t>
+  </si>
+  <si>
+    <t>If the policyRule is absent, computable consent would need to be constructed from the elements of the Consent resource.</t>
+  </si>
+  <si>
+    <t>Might be a unique identifier of a policy set in XACML, or other rules engine.</t>
+  </si>
+  <si>
+    <t>Regulatory policy examples.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/consent-policy|4.0.1</t>
+  </si>
+  <si>
+    <t>Consent.verification</t>
+  </si>
+  <si>
+    <t>Consent Verified by patient or family</t>
+  </si>
+  <si>
+    <t>Whether a treatment instruction (e.g. artificial respiration yes or no) was verified with the patient, his/her family or another authorized person.</t>
+  </si>
+  <si>
+    <t>Consent.verification.id</t>
+  </si>
+  <si>
+    <t>Consent.verification.extension</t>
+  </si>
+  <si>
+    <t>Consent.verification.modifierExtension</t>
+  </si>
+  <si>
+    <t>Consent.verification.verified</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
 </t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Consent.scope.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>Consent.category</t>
-  </si>
-  <si>
-    <t>Classification of the consent statement - for indexing/retrieval</t>
-  </si>
-  <si>
-    <t>A classification of the type of consents found in the statement. This element supports indexing and retrieval of consent statements.</t>
-  </si>
-  <si>
-    <t>A classification of the type of consents found in a consent statement.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-category|4.0.1</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>HL7 Table 0497 - Consent Type</t>
-  </si>
-  <si>
-    <t>CNTRCT</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Consent.patient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Who the consent applies to</t>
-  </si>
-  <si>
-    <t>The patient/healthcare consumer to whom this consent applies.</t>
-  </si>
-  <si>
-    <t>Commonly, the patient the consent pertains to is the author, but for young and old people, it may be some other person.</t>
-  </si>
-  <si>
-    <t>Event.subject</t>
-  </si>
-  <si>
-    <t>Role</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>Consent.dateTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Date de la directive anticipée</t>
-  </si>
-  <si>
-    <t>When this  Consent was issued / created / indexed.</t>
-  </si>
-  <si>
-    <t>This is not the time of the original consent, but the time that this statement was made or derived.</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>Field 13/ Consent Decision Date</t>
-  </si>
-  <si>
-    <t>FinancialConsent effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>Consent.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">consentor
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|RelatedPerson|4.0.1|PractitionerRole|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Who is agreeing to the policy and rules</t>
-  </si>
-  <si>
-    <t>Either the Grantor, which is the entity responsible for granting the rights listed in a Consent Directive or the Grantee, which is the entity responsible for complying with the Consent Directive, including any obligations or limitations on authorizations and enforcement of prohibitions.</t>
-  </si>
-  <si>
-    <t>Commonly, the patient the consent pertains to is the consentor, but particularly for young and old people, it may be some other person - e.g. a legal guardian.</t>
-  </si>
-  <si>
-    <t>Event.performer</t>
-  </si>
-  <si>
-    <t>Field 24/ ConsenterID</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>Consent.organization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">custodian
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Custodian of the consent</t>
-  </si>
-  <si>
-    <t>The organization that manages the consent, and the framework within which it is executed.</t>
-  </si>
-  <si>
-    <t>FiveWs.witness</t>
-  </si>
-  <si>
-    <t>Consent.source[x]</t>
-  </si>
-  <si>
-    <t>Attachment
-Reference(Consent|4.0.1|DocumentReference|4.0.1|Contract|4.0.1|QuestionnaireResponse|4.0.1)</t>
-  </si>
-  <si>
-    <t>Documents</t>
-  </si>
-  <si>
-    <t>The source on which this consent statement is based. The source might be a scanned original paper form, or a reference to a consent that links back to such a source, a reference to a document repository (e.g. XDS) that stores the original consent document.</t>
-  </si>
-  <si>
-    <t>The source can be contained inline (Attachment), referenced directly (Consent), referenced in a consent repository (DocumentReference), or simply by an identifier (Identifier), e.g. a CDA document id.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>Field 19 Informational Material Supplied Indicator</t>
-  </si>
-  <si>
-    <t>Consent.source[x]:sourceReference</t>
-  </si>
-  <si>
-    <t>sourceReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-document-reference-document)
-</t>
-  </si>
-  <si>
-    <t>Référence à un document externe</t>
-  </si>
-  <si>
-    <t>Consent.source[x]:sourceAttachment</t>
-  </si>
-  <si>
-    <t>sourceAttachment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attachment
-</t>
-  </si>
-  <si>
-    <t>Document encapsulé en B64</t>
-  </si>
-  <si>
-    <t>Consent.source[x]:sourceAttachment.id</t>
-  </si>
-  <si>
-    <t>Consent.source[x].id</t>
-  </si>
-  <si>
-    <t>Consent.source[x]:sourceAttachment.extension</t>
-  </si>
-  <si>
-    <t>Consent.source[x].extension</t>
-  </si>
-  <si>
-    <t>Consent.source[x]:sourceAttachment.contentType</t>
-  </si>
-  <si>
-    <t>Consent.source[x].contentType</t>
-  </si>
-  <si>
-    <t>Mime type of the content, with charset etc.</t>
-  </si>
-  <si>
-    <t>Identifies the type of the data in the attachment and allows a method to be chosen to interpret or render the data. Includes mime type parameters such as charset where appropriate.</t>
-  </si>
-  <si>
-    <t>Processors of the data need to be able to know how to interpret the data.</t>
-  </si>
-  <si>
-    <t>text/plain; charset=UTF-8, image/png</t>
-  </si>
-  <si>
-    <t>The mime type of an attachment. Any valid mime type is allowed.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/mimetypes|4.0.1</t>
-  </si>
-  <si>
-    <t>Attachment.contentType</t>
-  </si>
-  <si>
-    <t>ED.2+ED.3/RP.2+RP.3. Note conversion may be needed if old style values are being used</t>
-  </si>
-  <si>
-    <t>./mediaType, ./charset</t>
-  </si>
-  <si>
-    <t>Consent.source[x]:sourceAttachment.language</t>
-  </si>
-  <si>
-    <t>Consent.source[x].language</t>
-  </si>
-  <si>
-    <t>Human language of the content (BCP-47)</t>
-  </si>
-  <si>
-    <t>The human language of the content. The value can be any valid value according to BCP 47.</t>
-  </si>
-  <si>
-    <t>Users need to be able to choose between the languages in a set of attachments.</t>
-  </si>
-  <si>
-    <t>en-AU</t>
-  </si>
-  <si>
-    <t>Attachment.language</t>
-  </si>
-  <si>
-    <t>./language</t>
-  </si>
-  <si>
-    <t>Consent.source[x]:sourceAttachment.data</t>
-  </si>
-  <si>
-    <t>Consent.source[x].data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">base64Binary
-</t>
-  </si>
-  <si>
-    <t>Representation en B64</t>
-  </si>
-  <si>
-    <t>The actual data of the attachment - a sequence of bytes, base64 encoded.</t>
-  </si>
-  <si>
-    <t>The base64-encoded data SHALL be expressed in the same character set as the base resource XML or JSON.</t>
-  </si>
-  <si>
-    <t>The data needs to able to be transmitted inline.</t>
-  </si>
-  <si>
-    <t>Attachment.data</t>
-  </si>
-  <si>
-    <t>ED.5</t>
-  </si>
-  <si>
-    <t>./data</t>
-  </si>
-  <si>
-    <t>Consent.source[x]:sourceAttachment.url</t>
-  </si>
-  <si>
-    <t>Consent.source[x].url</t>
-  </si>
-  <si>
-    <t xml:space="preserve">url
-</t>
-  </si>
-  <si>
-    <t>URI</t>
-  </si>
-  <si>
-    <t>A location where the data can be accessed.</t>
-  </si>
-  <si>
-    <t>If both data and url are provided, the url SHALL point to the same content as the data contains. Urls may be relative references or may reference transient locations such as a wrapping envelope using cid: though this has ramifications for using signatures. Relative URLs are interpreted relative to the service url, like a resource reference, rather than relative to the resource itself. If a URL is provided, it SHALL resolve to actual data.</t>
-  </si>
-  <si>
-    <t>The data needs to be transmitted by reference.</t>
-  </si>
-  <si>
-    <t>http://www.acme.com/logo-small.png</t>
-  </si>
-  <si>
-    <t>Attachment.url</t>
-  </si>
-  <si>
-    <t>RP.1+RP.2 - if they refer to a URL (see v2.6)</t>
-  </si>
-  <si>
-    <t>./reference/literal</t>
-  </si>
-  <si>
-    <t>Consent.source[x]:sourceAttachment.size</t>
-  </si>
-  <si>
-    <t>Consent.source[x].size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unsignedInt
-</t>
-  </si>
-  <si>
-    <t>Number of bytes of content (if url provided)</t>
-  </si>
-  <si>
-    <t>The number of bytes of data that make up this attachment (before base64 encoding, if that is done).</t>
-  </si>
-  <si>
-    <t>The number of bytes is redundant if the data is provided as a base64binary, but is useful if the data is provided as a url reference.</t>
-  </si>
-  <si>
-    <t>Representing the size allows applications to determine whether they should fetch the content automatically in advance, or refuse to fetch it at all.</t>
-  </si>
-  <si>
-    <t>Attachment.size</t>
-  </si>
-  <si>
-    <t>N/A (needs data type R3 proposal)</t>
-  </si>
-  <si>
-    <t>Consent.source[x]:sourceAttachment.hash</t>
-  </si>
-  <si>
-    <t>Consent.source[x].hash</t>
-  </si>
-  <si>
-    <t>Hash of the data (sha-1, base64ed)</t>
-  </si>
-  <si>
-    <t>The calculated hash of the data using SHA-1. Represented using base64.</t>
-  </si>
-  <si>
-    <t>The hash is calculated on the data prior to base64 encoding, if the data is based64 encoded. The hash is not intended to support digital signatures. Where protection against malicious threats a digital signature should be considered, see [Provenance.signature](http://hl7.org/fhir/R4/provenance-definitions.html#Provenance.signature) for mechanism to protect a resource with a digital signature.</t>
-  </si>
-  <si>
-    <t>Included so that applications can verify that the contents of a location have not changed due to technical failures (e.g., storage rot, transport glitch, incorrect version).</t>
-  </si>
-  <si>
-    <t>Attachment.hash</t>
-  </si>
-  <si>
-    <t>.integrityCheck[parent::ED/integrityCheckAlgorithm="SHA-1"]</t>
-  </si>
-  <si>
-    <t>Consent.source[x]:sourceAttachment.title</t>
-  </si>
-  <si>
-    <t>Consent.source[x].title</t>
-  </si>
-  <si>
-    <t>Label to display in place of the data</t>
-  </si>
-  <si>
-    <t>A label or set of text to display in place of the data.</t>
-  </si>
-  <si>
-    <t>Applications need a label to display to a human user in place of the actual data if the data cannot be rendered or perceived by the viewer.</t>
-  </si>
-  <si>
-    <t>Official Corporate Logo</t>
-  </si>
-  <si>
-    <t>Attachment.title</t>
-  </si>
-  <si>
-    <t>./title/data</t>
-  </si>
-  <si>
-    <t>Consent.source[x]:sourceAttachment.creation</t>
-  </si>
-  <si>
-    <t>Consent.source[x].creation</t>
-  </si>
-  <si>
-    <t>Date attachment was first created</t>
-  </si>
-  <si>
-    <t>The date that the attachment was first created.</t>
-  </si>
-  <si>
-    <t>This is often tracked as an integrity issue for use of the attachment.</t>
-  </si>
-  <si>
-    <t>Attachment.creation</t>
-  </si>
-  <si>
-    <t>Consent.policy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Policies covered by this consent</t>
-  </si>
-  <si>
-    <t>The references to the policies that are included in this consent scope. Policies may be organizational, but are often defined jurisdictionally, or in law.</t>
-  </si>
-  <si>
-    <t>Consent.policy.id</t>
-  </si>
-  <si>
-    <t>Consent.policy.extension</t>
-  </si>
-  <si>
-    <t>Consent.policy.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>Consent.policy.authority</t>
-  </si>
-  <si>
-    <t>Enforcement source for policy</t>
-  </si>
-  <si>
-    <t>Entity or Organization having regulatory jurisdiction or accountability for  enforcing policies pertaining to Consent Directives.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ppc-1
-</t>
-  </si>
-  <si>
-    <t>Consent.policy.uri</t>
-  </si>
-  <si>
-    <t>Specific policy covered by this consent</t>
-  </si>
-  <si>
-    <t>This element is for discoverability / documentation and does not modify or qualify the policy rules.</t>
-  </si>
-  <si>
-    <t>Consent.policyRule</t>
-  </si>
-  <si>
-    <t>Regulation that this consents to</t>
-  </si>
-  <si>
-    <t>A reference to the specific base computable regulation or policy.</t>
-  </si>
-  <si>
-    <t>If the policyRule is absent, computable consent would need to be constructed from the elements of the Consent resource.</t>
-  </si>
-  <si>
-    <t>Might be a unique identifier of a policy set in XACML, or other rules engine.</t>
-  </si>
-  <si>
-    <t>Regulatory policy examples.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-policy|4.0.1</t>
-  </si>
-  <si>
-    <t>Consent.verification</t>
-  </si>
-  <si>
-    <t>Consent Verified by patient or family</t>
-  </si>
-  <si>
-    <t>Whether a treatment instruction (e.g. artificial respiration yes or no) was verified with the patient, his/her family or another authorized person.</t>
-  </si>
-  <si>
-    <t>Consent.verification.id</t>
-  </si>
-  <si>
-    <t>Consent.verification.extension</t>
-  </si>
-  <si>
-    <t>Consent.verification.modifierExtension</t>
-  </si>
-  <si>
-    <t>Consent.verification.verified</t>
   </si>
   <si>
     <t>Has been verified</t>
@@ -1458,6 +1283,10 @@
   </si>
   <si>
     <t>Consent.provision.securityLabel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
   </si>
   <si>
     <t>Security Labels that define affected resources</t>
@@ -1910,7 +1739,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN82"/>
+  <dimension ref="A1:AN71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.65625" customWidth="true" bestFit="true"/>
@@ -3492,7 +3321,7 @@
         <v>77</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>77</v>
@@ -3507,13 +3336,13 @@
         <v>77</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>77</v>
@@ -3560,10 +3389,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3571,10 +3400,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>77</v>
@@ -3583,10 +3412,10 @@
         <v>77</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="L15" t="s" s="2">
         <v>181</v>
@@ -3619,13 +3448,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>77</v>
+        <v>184</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3643,50 +3472,50 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>77</v>
+        <v>185</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>77</v>
+        <v>186</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>77</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>77</v>
@@ -3695,19 +3524,19 @@
         <v>77</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>135</v>
+        <v>190</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>136</v>
+        <v>191</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>138</v>
+        <v>193</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3745,16 +3574,16 @@
         <v>77</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>187</v>
+        <v>77</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>188</v>
+        <v>77</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>189</v>
@@ -3763,33 +3592,33 @@
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>77</v>
+        <v>194</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>77</v>
+        <v>196</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3800,10 +3629,10 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>77</v>
@@ -3812,20 +3641,18 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>195</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>77</v>
       </c>
@@ -3873,13 +3700,13 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>77</v>
@@ -3888,35 +3715,35 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>77</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>77</v>
+        <v>207</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>77</v>
@@ -3925,18 +3752,20 @@
         <v>77</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3985,43 +3814,43 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>77</v>
+        <v>212</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>77</v>
+        <v>213</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>77</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>134</v>
+        <v>216</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4037,20 +3866,18 @@
         <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>135</v>
+        <v>217</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>136</v>
+        <v>218</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -4087,19 +3914,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>187</v>
+        <v>77</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>188</v>
+        <v>77</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4111,27 +3938,27 @@
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>77</v>
+        <v>212</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>77</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4154,20 +3981,18 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>103</v>
+        <v>222</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
@@ -4176,7 +4001,7 @@
         <v>77</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>206</v>
+        <v>77</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>77</v>
@@ -4203,19 +4028,17 @@
         <v>77</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="AC20" s="2"/>
       <c r="AD20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>77</v>
+        <v>227</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4233,23 +4056,25 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>209</v>
+        <v>77</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>77</v>
       </c>
@@ -4261,7 +4086,7 @@
         <v>89</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>77</v>
@@ -4270,16 +4095,16 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>180</v>
+        <v>231</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4329,7 +4154,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4347,23 +4172,25 @@
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>216</v>
+        <v>77</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>77</v>
       </c>
@@ -4375,7 +4202,7 @@
         <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>77</v>
@@ -4384,18 +4211,18 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>109</v>
+        <v>235</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>77</v>
       </c>
@@ -4404,46 +4231,46 @@
         <v>77</v>
       </c>
       <c r="S22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="T22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4461,10 +4288,10 @@
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>224</v>
+        <v>77</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -4472,10 +4299,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4495,21 +4322,19 @@
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>180</v>
+        <v>239</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>228</v>
-      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>77</v>
       </c>
@@ -4518,7 +4343,7 @@
         <v>77</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>229</v>
+        <v>77</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>77</v>
@@ -4557,7 +4382,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4569,16 +4394,16 @@
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>231</v>
+        <v>77</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -4586,21 +4411,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>77</v>
@@ -4609,23 +4434,21 @@
         <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>234</v>
+        <v>135</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>235</v>
+        <v>136</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>77</v>
       </c>
@@ -4661,40 +4484,40 @@
         <v>77</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>77</v>
+        <v>247</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>77</v>
+        <v>248</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>240</v>
+        <v>77</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4702,10 +4525,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4728,19 +4551,17 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>180</v>
+        <v>109</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4753,7 +4574,7 @@
         <v>77</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>77</v>
+        <v>255</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>77</v>
@@ -4765,13 +4586,13 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>77</v>
+        <v>256</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>77</v>
+        <v>257</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
@@ -4789,7 +4610,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4807,10 +4628,10 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
@@ -4818,10 +4639,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4829,10 +4650,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G26" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="G26" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4844,16 +4665,18 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>173</v>
+        <v>109</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+      <c r="O26" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
       </c>
@@ -4865,7 +4688,7 @@
         <v>77</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>77</v>
+        <v>266</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>77</v>
@@ -4877,13 +4700,13 @@
         <v>77</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>176</v>
+        <v>113</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>253</v>
+        <v>114</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>254</v>
+        <v>115</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>77</v>
@@ -4901,13 +4724,13 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="AG26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH26" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
@@ -4916,24 +4739,24 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>255</v>
+        <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>256</v>
+        <v>77</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>258</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4953,21 +4776,23 @@
         <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
       </c>
@@ -5015,7 +4840,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5030,24 +4855,24 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>264</v>
+        <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>77</v>
+        <v>277</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>266</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5061,7 +4886,7 @@
         <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>77</v>
@@ -5070,18 +4895,20 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
@@ -5093,7 +4920,7 @@
         <v>77</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>77</v>
+        <v>286</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>77</v>
@@ -5129,7 +4956,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5144,35 +4971,35 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>272</v>
+        <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>275</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>277</v>
+        <v>77</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
@@ -5184,18 +5011,20 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
       </c>
@@ -5243,13 +5072,13 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
@@ -5258,35 +5087,35 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>282</v>
+        <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>283</v>
+        <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>77</v>
+        <v>298</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>284</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>286</v>
+        <v>77</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
@@ -5298,16 +5127,20 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
       </c>
@@ -5355,13 +5188,13 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
@@ -5370,24 +5203,24 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>282</v>
+        <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>77</v>
+        <v>306</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>290</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5410,18 +5243,18 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>292</v>
+        <v>239</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
       </c>
@@ -5433,7 +5266,7 @@
         <v>77</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>77</v>
+        <v>312</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>77</v>
@@ -5457,17 +5290,19 @@
         <v>77</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AC31" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>297</v>
+        <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5485,25 +5320,23 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>298</v>
+        <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>77</v>
+        <v>314</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>77</v>
       </c>
@@ -5515,7 +5348,7 @@
         <v>89</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>77</v>
@@ -5524,18 +5357,18 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>301</v>
+        <v>198</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
       </c>
@@ -5583,7 +5416,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>291</v>
+        <v>320</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5601,25 +5434,23 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AM32" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>77</v>
       </c>
@@ -5628,29 +5459,27 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5699,13 +5528,13 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>77</v>
@@ -5717,7 +5546,7 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>298</v>
+        <v>77</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5728,10 +5557,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5754,13 +5583,13 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>180</v>
+        <v>239</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>181</v>
+        <v>240</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>182</v>
+        <v>241</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5811,7 +5640,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>183</v>
+        <v>242</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5832,7 +5661,7 @@
         <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>184</v>
+        <v>243</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5840,10 +5669,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5872,7 +5701,7 @@
         <v>136</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>186</v>
+        <v>246</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>138</v>
@@ -5913,19 +5742,19 @@
         <v>77</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>187</v>
+        <v>77</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>188</v>
+        <v>77</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>189</v>
+        <v>249</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5946,7 +5775,7 @@
         <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>184</v>
+        <v>243</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5954,43 +5783,45 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>77</v>
+        <v>328</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O36" t="s" s="2">
-        <v>315</v>
+        <v>144</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -6003,7 +5834,7 @@
         <v>77</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>316</v>
+        <v>77</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>77</v>
@@ -6015,13 +5846,13 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>317</v>
+        <v>77</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>318</v>
+        <v>77</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -6039,28 +5870,28 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>320</v>
+        <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>321</v>
+        <v>132</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -6068,10 +5899,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6091,21 +5922,19 @@
         <v>77</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="N37" s="2"/>
-      <c r="O37" t="s" s="2">
-        <v>326</v>
-      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
       </c>
@@ -6117,7 +5946,7 @@
         <v>77</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>327</v>
+        <v>77</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>77</v>
@@ -6129,13 +5958,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -6153,7 +5982,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6162,7 +5991,7 @@
         <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>77</v>
+        <v>335</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>101</v>
@@ -6174,7 +6003,7 @@
         <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>329</v>
+        <v>77</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -6182,10 +6011,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6208,20 +6037,18 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>332</v>
+        <v>103</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
       </c>
@@ -6269,7 +6096,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6278,7 +6105,7 @@
         <v>89</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>77</v>
+        <v>335</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>101</v>
@@ -6287,10 +6114,10 @@
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>338</v>
+        <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>339</v>
+        <v>77</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6298,10 +6125,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6324,19 +6151,19 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6349,7 +6176,7 @@
         <v>77</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>347</v>
+        <v>77</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>77</v>
@@ -6361,13 +6188,13 @@
         <v>77</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>77</v>
+        <v>344</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>77</v>
+        <v>345</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
@@ -6385,7 +6212,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6394,7 +6221,7 @@
         <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>77</v>
+        <v>335</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>101</v>
@@ -6403,10 +6230,10 @@
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>349</v>
+        <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>350</v>
+        <v>77</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6414,10 +6241,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6428,7 +6255,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>77</v>
@@ -6440,20 +6267,16 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>353</v>
+        <v>322</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
       </c>
@@ -6501,13 +6324,13 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>77</v>
@@ -6522,7 +6345,7 @@
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>359</v>
+        <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6530,10 +6353,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6553,23 +6376,19 @@
         <v>77</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>332</v>
+        <v>239</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>362</v>
+        <v>240</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>365</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
       </c>
@@ -6617,7 +6436,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>366</v>
+        <v>242</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6629,7 +6448,7 @@
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
@@ -6638,7 +6457,7 @@
         <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>367</v>
+        <v>243</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6646,21 +6465,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>77</v>
@@ -6669,21 +6488,21 @@
         <v>77</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>370</v>
+        <v>136</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6695,7 +6514,7 @@
         <v>77</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>373</v>
+        <v>77</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>77</v>
@@ -6731,19 +6550,19 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>374</v>
+        <v>249</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
@@ -6752,7 +6571,7 @@
         <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>375</v>
+        <v>243</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>77</v>
@@ -6760,43 +6579,45 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>376</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>377</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>77</v>
+        <v>328</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>268</v>
+        <v>135</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>378</v>
+        <v>329</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O43" t="s" s="2">
-        <v>380</v>
+        <v>144</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6845,19 +6666,19 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>381</v>
+        <v>331</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6866,7 +6687,7 @@
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>359</v>
+        <v>132</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -6874,10 +6695,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>382</v>
+        <v>352</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>382</v>
+        <v>352</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6885,10 +6706,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>77</v>
@@ -6897,16 +6718,16 @@
         <v>77</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>383</v>
+        <v>353</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>384</v>
+        <v>354</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>385</v>
+        <v>355</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6957,13 +6778,13 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>382</v>
+        <v>352</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
@@ -6986,10 +6807,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>386</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>386</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7012,13 +6833,13 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>180</v>
+        <v>357</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>181</v>
+        <v>358</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>182</v>
+        <v>359</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7069,7 +6890,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>183</v>
+        <v>356</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7081,7 +6902,7 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
@@ -7090,7 +6911,7 @@
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -7098,21 +6919,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>387</v>
+        <v>360</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>387</v>
+        <v>360</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -7124,17 +6945,15 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>135</v>
+        <v>198</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>136</v>
+        <v>361</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -7183,19 +7002,19 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>189</v>
+        <v>360</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
@@ -7204,54 +7023,50 @@
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>389</v>
+        <v>77</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>135</v>
+        <v>322</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>390</v>
+        <v>364</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
       </c>
@@ -7299,19 +7114,19 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>392</v>
+        <v>363</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
@@ -7320,7 +7135,7 @@
         <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -7328,10 +7143,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>393</v>
+        <v>366</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>393</v>
+        <v>366</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7354,13 +7169,13 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>103</v>
+        <v>239</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>394</v>
+        <v>240</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>395</v>
+        <v>241</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7411,7 +7226,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>393</v>
+        <v>242</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7420,10 +7235,10 @@
         <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>396</v>
+        <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
@@ -7432,7 +7247,7 @@
         <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7440,21 +7255,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>397</v>
+        <v>367</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>397</v>
+        <v>367</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
@@ -7466,16 +7281,16 @@
         <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>398</v>
+        <v>136</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>385</v>
+        <v>246</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>399</v>
+        <v>138</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7525,19 +7340,19 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>397</v>
+        <v>249</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>396</v>
+        <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
@@ -7546,7 +7361,7 @@
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7554,45 +7369,45 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>400</v>
+        <v>368</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>400</v>
+        <v>368</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>77</v>
+        <v>328</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>401</v>
+        <v>329</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>402</v>
+        <v>330</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>403</v>
+        <v>138</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>404</v>
+        <v>144</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7617,13 +7432,13 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>405</v>
+        <v>77</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>406</v>
+        <v>77</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -7641,19 +7456,19 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>400</v>
+        <v>331</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>396</v>
+        <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
@@ -7662,7 +7477,7 @@
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7670,10 +7485,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>407</v>
+        <v>369</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>407</v>
+        <v>369</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7684,7 +7499,7 @@
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>77</v>
@@ -7696,13 +7511,13 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>383</v>
+        <v>109</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>408</v>
+        <v>370</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>409</v>
+        <v>371</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7729,13 +7544,13 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>77</v>
+        <v>372</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>77</v>
+        <v>373</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -7753,13 +7568,13 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>407</v>
+        <v>369</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>77</v>
@@ -7782,10 +7597,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>410</v>
+        <v>374</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>410</v>
+        <v>374</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7805,16 +7620,16 @@
         <v>77</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>180</v>
+        <v>375</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>181</v>
+        <v>376</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>182</v>
+        <v>377</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7865,7 +7680,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>183</v>
+        <v>374</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7877,7 +7692,7 @@
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
@@ -7886,7 +7701,7 @@
         <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -7894,14 +7709,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>411</v>
+        <v>378</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>411</v>
+        <v>378</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7920,22 +7735,22 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>135</v>
+        <v>322</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>136</v>
+        <v>379</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q53" s="2"/>
+      <c r="Q53" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="R53" t="s" s="2">
         <v>77</v>
       </c>
@@ -7979,7 +7794,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>189</v>
+        <v>378</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7991,7 +7806,7 @@
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
@@ -8000,7 +7815,7 @@
         <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -8008,46 +7823,42 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>412</v>
+        <v>382</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>412</v>
+        <v>382</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>389</v>
+        <v>77</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>135</v>
+        <v>239</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>390</v>
+        <v>240</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>77</v>
       </c>
@@ -8095,19 +7906,19 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>392</v>
+        <v>242</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
@@ -8116,7 +7927,7 @@
         <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>132</v>
+        <v>243</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -8124,21 +7935,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>413</v>
+        <v>383</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>413</v>
+        <v>383</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>77</v>
@@ -8147,18 +7958,20 @@
         <v>77</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>234</v>
+        <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>414</v>
+        <v>136</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8207,19 +8020,19 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>413</v>
+        <v>249</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
@@ -8228,7 +8041,7 @@
         <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -8236,42 +8049,46 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>416</v>
+        <v>384</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>416</v>
+        <v>384</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>77</v>
+        <v>328</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>417</v>
+        <v>135</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>418</v>
+        <v>329</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
       </c>
@@ -8319,19 +8136,19 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>416</v>
+        <v>331</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
@@ -8340,7 +8157,7 @@
         <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8348,10 +8165,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>420</v>
+        <v>385</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>420</v>
+        <v>385</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8359,7 +8176,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>89</v>
@@ -8374,13 +8191,13 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>268</v>
+        <v>173</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>421</v>
+        <v>386</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>422</v>
+        <v>387</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8407,13 +8224,13 @@
         <v>77</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>77</v>
+        <v>388</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>77</v>
+        <v>389</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>77</v>
@@ -8431,10 +8248,10 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>420</v>
+        <v>385</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>89</v>
@@ -8458,12 +8275,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>423</v>
+        <v>390</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>423</v>
+        <v>390</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8471,28 +8288,28 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>424</v>
+        <v>392</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>425</v>
+        <v>393</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8543,10 +8360,10 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>423</v>
+        <v>390</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>89</v>
@@ -8572,10 +8389,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>426</v>
+        <v>394</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>426</v>
+        <v>394</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8586,7 +8403,7 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>77</v>
@@ -8595,23 +8412,27 @@
         <v>77</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>181</v>
+        <v>395</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q59" s="2"/>
+      <c r="Q59" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="R59" t="s" s="2">
         <v>77</v>
       </c>
@@ -8631,13 +8452,13 @@
         <v>77</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>77</v>
+        <v>399</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>77</v>
+        <v>400</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>77</v>
+        <v>401</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>77</v>
@@ -8655,19 +8476,19 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>183</v>
+        <v>394</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
@@ -8676,7 +8497,7 @@
         <v>77</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>77</v>
@@ -8684,14 +8505,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>427</v>
+        <v>402</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>427</v>
+        <v>402</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8707,19 +8528,19 @@
         <v>77</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>135</v>
+        <v>403</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>136</v>
+        <v>404</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>186</v>
+        <v>405</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>138</v>
+        <v>406</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8745,13 +8566,13 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>77</v>
+        <v>407</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>77</v>
+        <v>408</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
@@ -8769,7 +8590,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>189</v>
+        <v>402</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8781,7 +8602,7 @@
         <v>77</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
@@ -8790,7 +8611,7 @@
         <v>77</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -8798,14 +8619,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>389</v>
+        <v>77</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8818,26 +8639,24 @@
         <v>77</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J61" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>135</v>
+        <v>403</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>77</v>
       </c>
@@ -8861,13 +8680,13 @@
         <v>77</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>77</v>
+        <v>413</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>77</v>
+        <v>414</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>77</v>
@@ -8885,7 +8704,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>392</v>
+        <v>409</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8897,7 +8716,7 @@
         <v>77</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>77</v>
@@ -8906,7 +8725,7 @@
         <v>77</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>77</v>
@@ -8914,10 +8733,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8928,7 +8747,7 @@
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>77</v>
@@ -8940,15 +8759,17 @@
         <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>109</v>
+        <v>403</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -8973,13 +8794,13 @@
         <v>77</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>77</v>
@@ -8997,13 +8818,13 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>77</v>
@@ -9026,10 +8847,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9040,7 +8861,7 @@
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>77</v>
@@ -9052,15 +8873,17 @@
         <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>435</v>
+        <v>173</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9085,13 +8908,11 @@
         <v>77</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>77</v>
+        <v>425</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>77</v>
@@ -9109,13 +8930,13 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>77</v>
@@ -9138,10 +8959,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9152,7 +8973,7 @@
         <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>77</v>
@@ -9161,25 +8982,25 @@
         <v>77</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q64" t="s" s="2">
-        <v>441</v>
-      </c>
+      <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
         <v>77</v>
       </c>
@@ -9223,13 +9044,13 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>77</v>
@@ -9252,10 +9073,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9266,7 +9087,7 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>77</v>
@@ -9275,23 +9096,25 @@
         <v>77</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>180</v>
+        <v>322</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>181</v>
+        <v>431</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>182</v>
+        <v>432</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q65" s="2"/>
+      <c r="Q65" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="R65" t="s" s="2">
         <v>77</v>
       </c>
@@ -9335,19 +9158,19 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>183</v>
+        <v>430</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
@@ -9356,7 +9179,7 @@
         <v>77</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>77</v>
@@ -9364,21 +9187,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>77</v>
@@ -9390,17 +9213,15 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>135</v>
+        <v>239</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>136</v>
+        <v>240</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -9449,19 +9270,19 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>189</v>
+        <v>242</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
@@ -9470,7 +9291,7 @@
         <v>77</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>184</v>
+        <v>243</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>77</v>
@@ -9478,14 +9299,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>389</v>
+        <v>134</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9498,26 +9319,24 @@
         <v>77</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>390</v>
+        <v>136</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>391</v>
+        <v>246</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="O67" t="s" s="2">
-        <v>144</v>
-      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>77</v>
       </c>
@@ -9565,7 +9384,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>392</v>
+        <v>249</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9586,7 +9405,7 @@
         <v>77</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>132</v>
+        <v>243</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>77</v>
@@ -9594,42 +9413,46 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>77</v>
+        <v>328</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>446</v>
+        <v>329</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
       </c>
@@ -9653,13 +9476,13 @@
         <v>77</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>448</v>
+        <v>77</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>449</v>
+        <v>77</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>77</v>
@@ -9677,19 +9500,19 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>445</v>
+        <v>331</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
@@ -9698,7 +9521,7 @@
         <v>77</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>77</v>
@@ -9706,10 +9529,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9729,16 +9552,16 @@
         <v>77</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>451</v>
+        <v>109</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9765,13 +9588,13 @@
         <v>77</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>77</v>
+        <v>440</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>77</v>
+        <v>441</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -9789,7 +9612,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>89</v>
@@ -9818,10 +9641,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9829,10 +9652,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>77</v>
@@ -9844,24 +9667,20 @@
         <v>90</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>173</v>
+        <v>443</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q70" t="s" s="2">
-        <v>458</v>
-      </c>
+      <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
         <v>77</v>
       </c>
@@ -9881,13 +9700,13 @@
         <v>77</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>459</v>
+        <v>77</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>460</v>
+        <v>77</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>461</v>
+        <v>77</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>77</v>
@@ -9905,13 +9724,13 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>77</v>
@@ -9934,10 +9753,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9957,20 +9776,18 @@
         <v>77</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>191</v>
+        <v>80</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9995,13 +9812,13 @@
         <v>77</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>466</v>
+        <v>77</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>467</v>
+        <v>77</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>77</v>
@@ -10019,7 +9836,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10046,1254 +9863,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="O72" s="2"/>
-      <c r="P72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="O74" s="2"/>
-      <c r="P74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="Y74" s="2"/>
-      <c r="Z74" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="O75" s="2"/>
-      <c r="P75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
-      <c r="P76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q76" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="R76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
-      <c r="P77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="78" hidden="true">
-      <c r="A78" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O78" s="2"/>
-      <c r="P78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="79" hidden="true">
-      <c r="A79" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="P79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
-      <c r="P80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="82" hidden="true">
-      <c r="A82" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
-      <c r="P82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AN82">
+  <autoFilter ref="A1:AN71">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11303,7 +9874,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI81">
+  <conditionalFormatting sqref="A2:AI70">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T15:31:02+00:00</t>
+    <t>2026-06-16T14:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:27:29+00:00</t>
+    <t>2026-06-18T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/main/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:40:49+00:00</t>
+    <t>2026-06-22T09:35:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
